--- a/results/canaliculi/682_z23c-2/measurements.xlsx
+++ b/results/canaliculi/682_z23c-2/measurements.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>58.6364</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>49.0825</v>
+        <v>48.7263</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>148.9507</v>
+        <v>156.9116</v>
       </c>
       <c r="C7" t="n">
-        <v>109.0968</v>
+        <v>110.1509</v>
       </c>
       <c r="D7" t="n">
-        <v>75.6772</v>
+        <v>73.7953</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,13 +849,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1328.2123</v>
+        <v>1700.5626</v>
       </c>
       <c r="D14" t="n">
-        <v>102.1702</v>
+        <v>100.0331</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -871,40 +871,18 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>414.7056</v>
+        <v>3084.2258</v>
       </c>
       <c r="D15" t="n">
-        <v>59.2437</v>
+        <v>110.1509</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>28</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3084.2258</v>
-      </c>
-      <c r="D16" t="n">
-        <v>110.1509</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>px</t>
         </is>

--- a/results/canaliculi/682_z23c-2/measurements.xlsx
+++ b/results/canaliculi/682_z23c-2/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.6364</v>
+        <v>38.4545</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>48.7263</v>
+        <v>33.1402</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156.9116</v>
+        <v>98.575</v>
       </c>
       <c r="C7" t="n">
-        <v>110.1509</v>
+        <v>54.7555</v>
       </c>
       <c r="D7" t="n">
-        <v>73.7953</v>
+        <v>83.6634</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>21426.4348</v>
+        <v>9347.284100000001</v>
       </c>
       <c r="D2" t="n">
-        <v>223.192</v>
+        <v>173.0979</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>13248.131</v>
+        <v>9483.140799999999</v>
       </c>
       <c r="D3" t="n">
-        <v>163.5572</v>
+        <v>172.4207</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>16389.9164</v>
+        <v>5291.7152</v>
       </c>
       <c r="D4" t="n">
-        <v>210.1271</v>
+        <v>115.0373</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>36811.3454</v>
+        <v>19611.2091</v>
       </c>
       <c r="D5" t="n">
-        <v>240.597</v>
+        <v>194.1704</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="C6" t="n">
-        <v>38706.8198</v>
+        <v>19613.0119</v>
       </c>
       <c r="D6" t="n">
-        <v>282.5315</v>
+        <v>222.8751</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>2692.4146</v>
+        <v>712.0681</v>
       </c>
       <c r="D7" t="n">
-        <v>107.6966</v>
+        <v>39.5593</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>22221.9037</v>
+        <v>17722.014</v>
       </c>
       <c r="D8" t="n">
-        <v>252.5216</v>
+        <v>249.6058</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>3409.8755</v>
+        <v>1531.259</v>
       </c>
       <c r="D9" t="n">
-        <v>94.7188</v>
+        <v>61.2504</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>5444.9335</v>
+        <v>1701.0063</v>
       </c>
       <c r="D10" t="n">
-        <v>170.1542</v>
+        <v>77.3185</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>5490.4625</v>
+        <v>1259.3768</v>
       </c>
       <c r="D11" t="n">
-        <v>133.9137</v>
+        <v>54.7555</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>1799.5921</v>
+        <v>280.7939</v>
       </c>
       <c r="D12" t="n">
-        <v>85.6949</v>
+        <v>28.0794</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -827,13 +837,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>2268.8957</v>
+        <v>373.9483</v>
       </c>
       <c r="D13" t="n">
-        <v>108.0427</v>
+        <v>31.1624</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -849,13 +859,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>1700.5626</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>100.0331</v>
+        <v>39.464</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -871,13 +881,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>3084.2258</v>
+        <v>773.8549</v>
       </c>
       <c r="D15" t="n">
-        <v>110.1509</v>
+        <v>48.3659</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z23c-2/measurements.xlsx
+++ b/results/canaliculi/682_z23c-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>38.4545</v>
-      </c>
-      <c r="C6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" t="n">
-        <v>33.1402</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>11</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>20.3636</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15.9579</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>653.3031</v>
+      </c>
+      <c r="C8" t="n">
+        <v>569.2030999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>470.9809</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>98.575</v>
-      </c>
-      <c r="C7" t="n">
-        <v>54.7555</v>
-      </c>
-      <c r="D7" t="n">
-        <v>83.6634</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>34.632</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33.2921</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.1993</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>9347.284100000001</v>
+        <v>294.2376</v>
       </c>
       <c r="D2" t="n">
-        <v>173.0979</v>
+        <v>19.6158</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9483.140799999999</v>
+        <v>16.2426</v>
       </c>
       <c r="D3" t="n">
-        <v>172.4207</v>
+        <v>8.1213</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>5291.7152</v>
+        <v>273.9949</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0373</v>
+        <v>30.4439</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>19611.2091</v>
+        <v>530.2153</v>
       </c>
       <c r="D5" t="n">
-        <v>194.1704</v>
+        <v>31.1891</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>19613.0119</v>
+        <v>618.1442</v>
       </c>
       <c r="D6" t="n">
-        <v>222.8751</v>
+        <v>32.5339</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>712.0681</v>
+        <v>176.2376</v>
       </c>
       <c r="D7" t="n">
-        <v>39.5593</v>
+        <v>35.2475</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>17722.014</v>
+        <v>1764.4794</v>
       </c>
       <c r="D8" t="n">
-        <v>249.6058</v>
+        <v>33.2921</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>1531.259</v>
+        <v>1140.2641</v>
       </c>
       <c r="D9" t="n">
-        <v>61.2504</v>
+        <v>24.7883</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>1701.0063</v>
+        <v>383.4214</v>
       </c>
       <c r="D10" t="n">
-        <v>77.3185</v>
+        <v>29.494</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>1259.3768</v>
+        <v>909.3818</v>
       </c>
       <c r="D11" t="n">
-        <v>54.7555</v>
+        <v>33.6808</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>280.7939</v>
+        <v>192.5391</v>
       </c>
       <c r="D12" t="n">
-        <v>28.0794</v>
+        <v>27.5056</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>373.9483</v>
+        <v>383.1615</v>
       </c>
       <c r="D13" t="n">
-        <v>31.1624</v>
+        <v>63.8602</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -859,13 +910,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>513.0315000000001</v>
+        <v>628.7128</v>
       </c>
       <c r="D14" t="n">
-        <v>39.464</v>
+        <v>34.9285</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -881,13 +932,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>773.8549</v>
+        <v>569.2030999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>48.3659</v>
+        <v>33.4825</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z23c-2/measurements.xlsx
+++ b/results/canaliculi/682_z23c-2/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.3636</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9579</v>
+        <v>27.5971</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>653.3031</v>
+        <v>1065.8168</v>
       </c>
       <c r="C8" t="n">
-        <v>569.2030999999999</v>
+        <v>920.8964999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>470.9809</v>
+        <v>819.2391</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.632</v>
+        <v>32.7335</v>
       </c>
       <c r="C9" t="n">
-        <v>33.2921</v>
+        <v>31.7551</v>
       </c>
       <c r="D9" t="n">
-        <v>10.1993</v>
+        <v>7.1512</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1022712</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>39168</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03829817</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>481</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00047032</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.369e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>756</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>51.8095</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -649,10 +850,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>294.2376</v>
+        <v>297.066</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6158</v>
+        <v>19.8044</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -693,10 +894,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>273.9949</v>
+        <v>278.9949</v>
       </c>
       <c r="D4" t="n">
-        <v>30.4439</v>
+        <v>30.9994</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>530.2153</v>
+        <v>1121.4306</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1891</v>
+        <v>26.7007</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>618.1442</v>
+        <v>1245.9747</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5339</v>
+        <v>23.509</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>176.2376</v>
+        <v>216.1076</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2475</v>
+        <v>36.0179</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -778,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1764.4794</v>
+        <v>1597.0113</v>
       </c>
       <c r="D8" t="n">
-        <v>33.2921</v>
+        <v>31.9402</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>1140.2641</v>
+        <v>3058.9049</v>
       </c>
       <c r="D9" t="n">
-        <v>24.7883</v>
+        <v>30.589</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>383.4214</v>
+        <v>1034.6661</v>
       </c>
       <c r="D10" t="n">
-        <v>29.494</v>
+        <v>29.5619</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -844,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>909.3818</v>
+        <v>920.8964999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>33.6808</v>
+        <v>31.7551</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -866,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>192.5391</v>
+        <v>486.0315</v>
       </c>
       <c r="D12" t="n">
-        <v>27.5056</v>
+        <v>37.387</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -888,13 +1089,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>383.1615</v>
+        <v>444.4457</v>
       </c>
       <c r="D13" t="n">
-        <v>63.8602</v>
+        <v>49.3829</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -910,13 +1111,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>628.7128</v>
+        <v>781.9382000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>34.9285</v>
+        <v>25.2238</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -932,13 +1133,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C15" t="n">
-        <v>569.2030999999999</v>
+        <v>1572.2489</v>
       </c>
       <c r="D15" t="n">
-        <v>33.4825</v>
+        <v>36.5639</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
